--- a/events/Poznan_2011_WC/Poznan_2011_WC_Results.xlsx
+++ b/events/Poznan_2011_WC/Poznan_2011_WC_Results.xlsx
@@ -787,6 +787,11 @@
           <t>1:55.526</t>
         </is>
       </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>36391</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1397,6 +1402,11 @@
           <t>2:00.892</t>
         </is>
       </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>36459</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3197,6 +3207,11 @@
           <t>3:34.798</t>
         </is>
       </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4947,6 +4962,11 @@
           <t>4:18.640</t>
         </is>
       </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>46101</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5442,6 +5462,11 @@
           <t>4:12.546</t>
         </is>
       </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>52756</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6136,6 +6161,11 @@
       <c r="L91" t="n">
         <v>9</v>
       </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>36496</t>
+        </is>
+      </c>
       <c r="X91" t="inlineStr">
         <is>
           <t>DSQ</t>
@@ -7755,6 +7785,11 @@
           <t>3:17.780</t>
         </is>
       </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -8450,6 +8485,11 @@
           <t>1:59.789</t>
         </is>
       </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>36459</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -8510,6 +8550,11 @@
           <t>2:00.437</t>
         </is>
       </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>36391</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -9750,6 +9795,11 @@
           <t>3:33.267</t>
         </is>
       </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -11050,6 +11100,11 @@
           <t>4:02.257</t>
         </is>
       </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>52756</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -11295,6 +11350,11 @@
           <t>4:22.469</t>
         </is>
       </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>46101</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -13270,6 +13330,11 @@
           <t>3:18.462</t>
         </is>
       </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -13780,6 +13845,11 @@
           <t>1:45.227</t>
         </is>
       </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -15762,6 +15832,11 @@
           <t>1:53.224</t>
         </is>
       </c>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -17061,6 +17136,11 @@
       <c r="L265" t="n">
         <v>7</v>
       </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>56336</t>
+        </is>
+      </c>
       <c r="X265" t="inlineStr">
         <is>
           <t>DSQ</t>
@@ -18371,6 +18451,11 @@
           <t>1:51.626</t>
         </is>
       </c>
+      <c r="R285" t="inlineStr">
+        <is>
+          <t>36496</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -19445,6 +19530,16 @@
           <t>52232</t>
         </is>
       </c>
+      <c r="T301" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>56336</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -20195,6 +20290,11 @@
           <t>1:43.870</t>
         </is>
       </c>
+      <c r="R313" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -23025,6 +23125,11 @@
           <t>1:48.605</t>
         </is>
       </c>
+      <c r="R358" t="inlineStr">
+        <is>
+          <t>36496</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -23285,6 +23390,16 @@
           <t>52232</t>
         </is>
       </c>
+      <c r="T362" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>56336</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -24303,6 +24418,11 @@
           <t>4:24.132</t>
         </is>
       </c>
+      <c r="R378" t="inlineStr">
+        <is>
+          <t>52756</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -25588,6 +25708,11 @@
           <t>2:05.656</t>
         </is>
       </c>
+      <c r="R398" t="inlineStr">
+        <is>
+          <t>36459</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -25701,6 +25826,11 @@
       <c r="L400" t="n">
         <v>9</v>
       </c>
+      <c r="R400" t="inlineStr">
+        <is>
+          <t>36391</t>
+        </is>
+      </c>
       <c r="X400" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -26897,6 +27027,11 @@
           <t>3:41.865</t>
         </is>
       </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -28986,6 +29121,11 @@
           <t>3:33.060</t>
         </is>
       </c>
+      <c r="R450" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -29871,6 +30011,11 @@
           <t>42059</t>
         </is>
       </c>
+      <c r="T463" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -30936,6 +31081,16 @@
           <t>52232</t>
         </is>
       </c>
+      <c r="T478" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
+      <c r="U478" t="inlineStr">
+        <is>
+          <t>56336</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -33865,6 +34020,11 @@
           <t>0:46.113</t>
         </is>
       </c>
+      <c r="R525" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -35115,6 +35275,11 @@
           <t>0:46.972</t>
         </is>
       </c>
+      <c r="R545" t="inlineStr">
+        <is>
+          <t>36496</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -35355,6 +35520,11 @@
           <t>0:43.218</t>
         </is>
       </c>
+      <c r="R549" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -36279,6 +36449,11 @@
           <t>0:48.988</t>
         </is>
       </c>
+      <c r="R564" t="inlineStr">
+        <is>
+          <t>52756</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -36399,6 +36574,11 @@
           <t>1:52.503</t>
         </is>
       </c>
+      <c r="R566" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -38204,6 +38384,11 @@
           <t>52232</t>
         </is>
       </c>
+      <c r="S594" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -40962,6 +41147,11 @@
           <t>0:51.496</t>
         </is>
       </c>
+      <c r="R638" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
@@ -42207,6 +42397,11 @@
           <t>0:43.888</t>
         </is>
       </c>
+      <c r="R658" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -42577,6 +42772,11 @@
           <t>0:45.788</t>
         </is>
       </c>
+      <c r="R664" t="inlineStr">
+        <is>
+          <t>36496</t>
+        </is>
+      </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
@@ -44047,6 +44247,11 @@
           <t>52232</t>
         </is>
       </c>
+      <c r="S687" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
@@ -46244,6 +46449,11 @@
           <t>52232</t>
         </is>
       </c>
+      <c r="S721" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
@@ -47879,6 +48089,11 @@
           <t>0:43.458</t>
         </is>
       </c>
+      <c r="R746" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
@@ -50524,6 +50739,11 @@
           <t>1:53.631</t>
         </is>
       </c>
+      <c r="R786" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
@@ -51318,6 +51538,11 @@
           <t>1:53.139</t>
         </is>
       </c>
+      <c r="R798" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
@@ -53005,6 +53230,11 @@
           <t>2:08.625</t>
         </is>
       </c>
+      <c r="R824" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
     </row>
     <row r="825">
       <c r="A825" t="inlineStr">
@@ -54551,6 +54781,11 @@
           <t>20:46.107</t>
         </is>
       </c>
+      <c r="R847" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
@@ -57260,6 +57495,11 @@
       <c r="P890" t="inlineStr">
         <is>
           <t>26:42.503</t>
+        </is>
+      </c>
+      <c r="R890" t="inlineStr">
+        <is>
+          <t>52756</t>
         </is>
       </c>
     </row>
@@ -57442,7 +57682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D136"/>
+  <dimension ref="A1:D147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60437,6 +60677,248 @@
         </is>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Jonathan</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>BOYTON</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>36391</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Bridgitte</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>HARTLEY</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>36459</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Joana</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>SOUSA</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>36496</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Ronny</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>RATIA</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Aleh</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>YURENIA</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Volha</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>KHUDZENKA</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Helder</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>SILVA</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>46101</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Johnnathan</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>TAFRA</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Aleksey</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>MOCHALOV</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>52756</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Shahou</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>NASERI</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>56336</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Vyacheslav</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>GORN</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Poznan_2011_WC/Poznan_2011_WC_Results.xlsx
+++ b/events/Poznan_2011_WC/Poznan_2011_WC_Results.xlsx
@@ -2032,6 +2032,11 @@
           <t>2:00.651</t>
         </is>
       </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>52610</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5782,6 +5787,11 @@
           <t>3:41.768</t>
         </is>
       </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>46354</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6641,6 +6651,11 @@
           <t>3:45.321</t>
         </is>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>46397</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7146,6 +7161,11 @@
           <t>36498</t>
         </is>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>36501</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -9110,6 +9130,11 @@
           <t>2:01.493</t>
         </is>
       </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>52610</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -12440,6 +12465,11 @@
           <t>3:45.985</t>
         </is>
       </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>46397</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -13655,6 +13685,11 @@
           <t>36498</t>
         </is>
       </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>36501</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -16772,6 +16807,11 @@
           <t>41991</t>
         </is>
       </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>42044</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -18046,6 +18086,11 @@
           <t>1:50.957</t>
         </is>
       </c>
+      <c r="R279" t="inlineStr">
+        <is>
+          <t>36501</t>
+        </is>
+      </c>
       <c r="S279" t="inlineStr">
         <is>
           <t>106229</t>
@@ -18980,6 +19025,11 @@
           <t>2:58.574</t>
         </is>
       </c>
+      <c r="R293" t="inlineStr">
+        <is>
+          <t>42046</t>
+        </is>
+      </c>
       <c r="U293" t="inlineStr">
         <is>
           <t>42049</t>
@@ -19250,6 +19300,11 @@
           <t>3:26.222</t>
         </is>
       </c>
+      <c r="R297" t="inlineStr">
+        <is>
+          <t>36501</t>
+        </is>
+      </c>
       <c r="S297" t="inlineStr">
         <is>
           <t>106229</t>
@@ -19325,6 +19380,11 @@
           <t>41991</t>
         </is>
       </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>42044</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -22420,6 +22480,11 @@
           <t>1:47.825</t>
         </is>
       </c>
+      <c r="R347" t="inlineStr">
+        <is>
+          <t>36501</t>
+        </is>
+      </c>
       <c r="S347" t="inlineStr">
         <is>
           <t>106229</t>
@@ -23525,6 +23590,11 @@
           <t>3:13.209</t>
         </is>
       </c>
+      <c r="R364" t="inlineStr">
+        <is>
+          <t>36501</t>
+        </is>
+      </c>
       <c r="S364" t="inlineStr">
         <is>
           <t>106229</t>
@@ -29878,6 +29948,11 @@
           <t>3:56.991</t>
         </is>
       </c>
+      <c r="R461" t="inlineStr">
+        <is>
+          <t>46354</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -30721,6 +30796,11 @@
           <t>41991</t>
         </is>
       </c>
+      <c r="U473" t="inlineStr">
+        <is>
+          <t>42044</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -30783,6 +30863,11 @@
           <t>3:11.696</t>
         </is>
       </c>
+      <c r="R474" t="inlineStr">
+        <is>
+          <t>42046</t>
+        </is>
+      </c>
       <c r="U474" t="inlineStr">
         <is>
           <t>42049</t>
@@ -34210,6 +34295,11 @@
           <t>0:48.421</t>
         </is>
       </c>
+      <c r="R528" t="inlineStr">
+        <is>
+          <t>52610</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -35460,6 +35550,11 @@
           <t>0:42.922</t>
         </is>
       </c>
+      <c r="R548" t="inlineStr">
+        <is>
+          <t>46354</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -37979,6 +38074,11 @@
           <t>0:39.484</t>
         </is>
       </c>
+      <c r="R588" t="inlineStr">
+        <is>
+          <t>36501</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
@@ -38584,6 +38684,11 @@
           <t>41991</t>
         </is>
       </c>
+      <c r="S597" t="inlineStr">
+        <is>
+          <t>42044</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
@@ -41592,6 +41697,11 @@
           <t>0:47.293</t>
         </is>
       </c>
+      <c r="R645" t="inlineStr">
+        <is>
+          <t>52610</t>
+        </is>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
@@ -43542,6 +43652,11 @@
           <t>41991</t>
         </is>
       </c>
+      <c r="S676" t="inlineStr">
+        <is>
+          <t>42044</t>
+        </is>
+      </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
@@ -43917,6 +44032,11 @@
           <t>0:39.481</t>
         </is>
       </c>
+      <c r="R682" t="inlineStr">
+        <is>
+          <t>36501</t>
+        </is>
+      </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
@@ -45541,6 +45661,11 @@
           <t>0:48.704</t>
         </is>
       </c>
+      <c r="R707" t="inlineStr">
+        <is>
+          <t>52610</t>
+        </is>
+      </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
@@ -47697,6 +47822,11 @@
           <t>0:42.654</t>
         </is>
       </c>
+      <c r="R740" t="inlineStr">
+        <is>
+          <t>46354</t>
+        </is>
+      </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
@@ -49146,6 +49276,11 @@
           <t>41991</t>
         </is>
       </c>
+      <c r="S762" t="inlineStr">
+        <is>
+          <t>42044</t>
+        </is>
+      </c>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
@@ -53560,6 +53695,11 @@
           <t>41991</t>
         </is>
       </c>
+      <c r="S829" t="inlineStr">
+        <is>
+          <t>42044</t>
+        </is>
+      </c>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
@@ -56788,6 +56928,11 @@
       <c r="P879" t="inlineStr">
         <is>
           <t>23:43.575</t>
+        </is>
+      </c>
+      <c r="R879" t="inlineStr">
+        <is>
+          <t>46397</t>
         </is>
       </c>
     </row>
@@ -57682,7 +57827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D147"/>
+  <dimension ref="A1:D153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60919,6 +61064,138 @@
         </is>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>52610</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Irina</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>PODOINKOVA</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>46354</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Yiuri</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>CHEBAN</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>46397</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Eduard</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>SHEMETILA</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>36501</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Jesus</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>COLMENARES</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>42044</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Vadzim</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>MAKHNEV</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>42046</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Pavel</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>MIADZVEDZEV</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Poznan_2011_WC/Poznan_2011_WC_Results.xlsx
+++ b/events/Poznan_2011_WC/Poznan_2011_WC_Results.xlsx
@@ -35305,6 +35305,11 @@
           <t>0:46.456</t>
         </is>
       </c>
+      <c r="R544" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -42127,6 +42132,11 @@
           <t>0:45.249</t>
         </is>
       </c>
+      <c r="R652" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
@@ -45793,6 +45803,11 @@
       <c r="P709" t="inlineStr">
         <is>
           <t>0:44.708</t>
+        </is>
+      </c>
+      <c r="R709" t="inlineStr">
+        <is>
+          <t>36633</t>
         </is>
       </c>
     </row>
@@ -57827,7 +57842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D153"/>
+  <dimension ref="A1:D154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61196,6 +61211,28 @@
         </is>
       </c>
     </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>NIVALTER</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>SANTOS DE JESUS</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
